--- a/home/src/Daily_Economic_Report_20260730.xlsx
+++ b/home/src/Daily_Economic_Report_20260730.xlsx
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1433.54</v>
+        <v>1433.84</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.35</v>
+        <v>-1.33</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>83.70999999999999</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.89</v>
+        <v>-1.18</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2881,7 +2881,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 10:20:07 GMT</t>
+          <t>Thu, 30 Jul 2026 07:46:51 GMT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>최태원 SK 회장, SK하이닉스 주식 3천620주 매입…"책임경영 일환"(상보)</t>
+          <t>"증시 비상사태" 질타에 당국도 비상…'공매도 금지' 만지작</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9aLTFGSVFwODFJVEF4dHRQY0loZ08xdEJlUTh2M0sxZ0JLSmlhTjR4emRCV3ZGRE9iUHdhckRBZE9URzNzZnduUWpfX28tRUtURkM3OHlXbVJPUFdodzdEZUNrX3VQaVU3WU5zUjdrV3U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1vNGs4eFdnREdOcTV3SjlOekRsRXZ6d2NjNHdDYlF5V3dPTUZSMDExcFdkNjlFbkFZRmFySFEzRDJiRTdJUzhpUnUwUUttVUdEbU9NbElpSEhkSkNQcV8wUkF0MnJYVGNfbDgzSFNYb3I?oc=5</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Wed, 29 Jul 2026 20:16:00 GMT</t>
+          <t>Thu, 30 Jul 2026 10:20:07 GMT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[뉴욕증시-1보] 워시 한 마디에 요동친 시장…급락 마감</t>
+          <t>최태원 SK 회장, SK하이닉스 주식 3천620주 매입…"책임경영 일환"(상보)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE80T1phRFJHRGYxSUFKeEJZazctYmFtNXJtT0FlZ2lESTNTZ1BuMGs0OEJwR2Qyam1TMTZpd0FaQ1NNN3o5b3I0X2J3S2FJZjB3UmV2c3dpMVh1eTR5d09UOWdCTy1Wc1J5NUl5d2xLd2nSAXRBVV95cUxPYVNsbW03OHNpSTNfbmJscE5nNUE3cWkxdDN4aU5PZDgyb1FRNjFTMDBEX0dWckNNelhiZWIzMk90VGE1YkRpX2FBV3htMWhRd19rcEpqOWVJcmdnMzRzX3VNOHB5Qnh5SXk2d1RwUTh6QnYwVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9aLTFGSVFwODFJVEF4dHRQY0loZ08xdEJlUTh2M0sxZ0JLSmlhTjR4emRCV3ZGRE9iUHdhckRBZE9URzNzZnduUWpfX28tRUtURkM3OHlXbVJPUFdodzdEZUNrX3VQaVU3WU5zUjdrV3U?oc=5</t>
         </is>
       </c>
     </row>
@@ -3178,54 +3178,54 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 10:31:00 GMT</t>
+          <t>Thu, 30 Jul 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ytn.co.kr</t>
+          <t>주간조선</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>최태원, SK하이닉스 주식 48억 원어치 장내 매수</t>
+          <t>증시 급등락에 뿔난 개미들 ‘국민과 주주’ 창당 선언</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>중립</t>
+          <t>긍정적 (호재)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBCb3dvWHdSMnRiMEhZUmN3VUJKdU9MczRtRmNUSGNRRDNGZlpWNEpCQ2xPWndYSmpEdWVIUXV0ek00ZXBsUGtzdHRPQkVQUzY5VlZ1UmJrVkpyYWhFbVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBfMV9nOEYxbFQxdk5menFWcXpnR19KcnlvaTZOX01tbEE5eDE5Q3dkbFMwd0owRXJ6OHdiTmRFMklkeE1ZNkJidGtrU3R0cFRQVlhsM0NQa0NWandxdkhINE42eVBmdFdzSXfSAW5BVV95cUxPaDRmRWZoZG55QWdSSWJPUnFvWjhlX3VkQ3cza3BDV0FKcmJNVjVLUmx3N29PM3puWFBLZ1hGdmtacFM2Mkc4eFFpaVFfZ3NsX3BpUU0yQktUWV9yeUtrQ2gzaGkxenZSQzlyLXpsZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 08:00:00 GMT</t>
+          <t>Thu, 30 Jul 2026 10:31:00 GMT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>주간조선</t>
+          <t>ytn.co.kr</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>증시 급등락에 뿔난 개미들 ‘국민과 주주’ 창당 선언</t>
+          <t>최태원, SK하이닉스 주식 48억 원어치 장내 매수</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>긍정적 (호재)</t>
+          <t>중립</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBfMV9nOEYxbFQxdk5menFWcXpnR19KcnlvaTZOX01tbEE5eDE5Q3dkbFMwd0owRXJ6OHdiTmRFMklkeE1ZNkJidGtrU3R0cFRQVlhsM0NQa0NWandxdkhINE42eVBmdFdzSXfSAW5BVV95cUxPaDRmRWZoZG55QWdSSWJPUnFvWjhlX3VkQ3cza3BDV0FKcmJNVjVLUmx3N29PM3puWFBLZ1hGdmtacFM2Mkc4eFFpaVFfZ3NsX3BpUU0yQktUWV9yeUtrQ2gzaGkxenZSQzlyLXpsZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBCb3dvWHdSMnRiMEhZUmN3VUJKdU9MczRtRmNUSGNRRDNGZlpWNEpCQ2xPWndYSmpEdWVIUXV0ek00ZXBsUGtzdHRPQkVQUzY5VlZ1UmJrVkpyYWhFbVE?oc=5</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 10:07:26 GMT</t>
+          <t>Wed, 29 Jul 2026 20:16:00 GMT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>최태원 SK 회장, SK하이닉스 주식 3천620주 장내 매수…48억원</t>
+          <t>[뉴욕증시-1보] 워시 한 마디에 요동친 시장…급락 마감</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1nVjRJZTE1Sm1JVmxrOGdLenYtWWhZa181VDRaMFBxRmFXUnUyNnNBNUVnNFNSODFvaUkxOFk4cUJtTWU2Q3dVUEI4TXMyX3VYenhrRFN2T3puVXFqTnFpX3hJdTgxczd6bV9CTkRqcm7SAXRBVV95cUxPVmN5a2NrUXYzT2t2U2ZXZzVzcDdFSEtKa3lEcEF1b0lXdS1NeFVOMmo0NkNaNEZWVmt1MDU2RjhCNkF2Z3EtcXJDc2lWbHJTU2pZLUdFYnBPNUpfbHZhVWtiRTJtTTBkQ2Zkc0IzTl9JRDNpZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE80T1phRFJHRGYxSUFKeEJZazctYmFtNXJtT0FlZ2lESTNTZ1BuMGs0OEJwR2Qyam1TMTZpd0FaQ1NNN3o5b3I0X2J3S2FJZjB3UmV2c3dpMVh1eTR5d09UOWdCTy1Wc1J5NUl5d2xLd2nSAXRBVV95cUxPYVNsbW03OHNpSTNfbmJscE5nNUE3cWkxdDN4aU5PZDgyb1FRNjFTMDBEX0dWckNNelhiZWIzMk90VGE1YkRpX2FBV3htMWhRd19rcEpqOWVJcmdnMzRzX3VNOHB5Qnh5SXk2d1RwUTh6QnYwVw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3313,27 +3313,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 10:55:02 GMT</t>
+          <t>Thu, 30 Jul 2026 10:07:26 GMT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>매일경제 마켓</t>
+          <t>연합인포맥스</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>빅테크 현금 마르고 시장금리 오르고…돌파구 못 찾는 반도체 투심[머니닥터 시장진단]</t>
+          <t>최태원 SK 회장, SK하이닉스 주식 3천620주 장내 매수…48억원</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>긍정적 (호재)</t>
+          <t>중립</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE1aVUY2TXdVREo5Rk1kOXhUUWt3SWk4N3dvZ2lpS0VUbDIzcHpjZ0Zkc3Fqd184R29iZmYwVlllUXVvVnNHNkduRnBmR2d3QnV1b1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1nVjRJZTE1Sm1JVmxrOGdLenYtWWhZa181VDRaMFBxRmFXUnUyNnNBNUVnNFNSODFvaUkxOFk4cUJtTWU2Q3dVUEI4TXMyX3VYenhrRFN2T3puVXFqTnFpX3hJdTgxczd6bV9CTkRqcm7SAXRBVV95cUxPVmN5a2NrUXYzT2t2U2ZXZzVzcDdFSEtKa3lEcEF1b0lXdS1NeFVOMmo0NkNaNEZWVmt1MDU2RjhCNkF2Z3EtcXJDc2lWbHJTU2pZLUdFYnBPNUpfbHZhVWtiRTJtTTBkQ2Zkc0IzTl9JRDNpZA?oc=5</t>
         </is>
       </c>
     </row>
@@ -3394,44 +3394,44 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 03:21:30 GMT</t>
+          <t>Thu, 30 Jul 2026 10:55:02 GMT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>hankyung.com</t>
+          <t>매일경제 마켓</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>"한국은 치고 나가는데"…'꼴찌 전락 위기' 日 초비상 [최만수의 재팬 인사이트]</t>
+          <t>빅테크 현금 마르고 시장금리 오르고…돌파구 못 찾는 반도체 투심[머니닥터 시장진단]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>부정적 (악재)</t>
+          <t>긍정적 (호재)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1yamZsdEZOdVpQZXFwZ09NU1dUamFGSkk0cTdERDNIeGE3RENoYlFzck5qQjFCSGNKemMtZEdkSk5XRWhuWF9OUThzX25tZmZpSTNtbmU3WWhMdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE1aVUY2TXdVREo5Rk1kOXhUUWt3SWk4N3dvZ2lpS0VUbDIzcHpjZ0Zkc3Fqd184R29iZmYwVlllUXVvVnNHNkduRnBmR2d3QnV1b1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 08:15:28 GMT</t>
+          <t>Thu, 30 Jul 2026 11:21:00 GMT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>yna.co.kr</t>
+          <t>v.daum.net</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AI 특수가 가른 中 지역 경제성장률…상반기 양극화 심화</t>
+          <t>최태원 회장, SK하이닉스 주식 3천620주 매수…약 48억원어치</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3441,24 +3441,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5TSnBkT3hWS2diaGM5WWpIZGxYcmU2ejdqU3RZWTlPamZ0WDJmNlB6cFR2NGpraXR3NGxfS3ZCZzFSMktaRjlKN1R6LTZ6MXFVd29SU1dWUWRNZjjSAWBBVV95cUxPenhaN3l1MDNLMzlfbWNrV3BPd19YZjZFaG5jUV9GX0VwMnlTNlFPblNYTEE3QWFkeVZuOGhJZ0p1SHQySlUxOUxMdHhIQ3FySmpkUHU5eVc2VDN5alFval8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE1LTWtQMXpiNXYwNHY0Ui1wT09sdGFlT0IyclpEdHRBX2xRRjMtNXFIZWdSdzh5WU5mRzFGWFcwZFM5WjFReHUxWVZlTFhhVnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 07:46:51 GMT</t>
+          <t>Thu, 30 Jul 2026 08:15:28 GMT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>연합인포맥스</t>
+          <t>yna.co.kr</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>"증시 비상사태" 질타에 당국도 비상…'공매도 금지' 만지작</t>
+          <t>AI 특수가 가른 中 지역 경제성장률…상반기 양극화 심화</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3468,105 +3468,105 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1vNGs4eFdnREdOcTV3SjlOekRsRXZ6d2NjNHdDYlF5V3dPTUZSMDExcFdkNjlFbkFZRmFySFEzRDJiRTdJUzhpUnUwUUttVUdEbU9NbElpSEhkSkNQcV8wUkF0MnJYVGNfbDgzSFNYb3I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5TSnBkT3hWS2diaGM5WWpIZGxYcmU2ejdqU3RZWTlPamZ0WDJmNlB6cFR2NGpraXR3NGxfS3ZCZzFSMktaRjlKN1R6LTZ6MXFVd29SU1dWUWRNZjjSAWBBVV95cUxPenhaN3l1MDNLMzlfbWNrV3BPd19YZjZFaG5jUV9GX0VwMnlTNlFPblNYTEE3QWFkeVZuOGhJZ0p1SHQySlUxOUxMdHhIQ3FySmpkUHU5eVc2VDN5alFval8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 10:24:52 GMT</t>
+          <t>Thu, 30 Jul 2026 03:21:30 GMT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>v.daum.net</t>
+          <t>hankyung.com</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>최태원, SK하이닉스 주식 48억 규모 장내매수…"책임경영 차원"</t>
+          <t>"한국은 치고 나가는데"…'꼴찌 전락 위기' 日 초비상 [최만수의 재팬 인사이트]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>중립</t>
+          <t>부정적 (악재)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE1URXB1M3dRWmlhbjJJYy05S053U1c5WG5pVnJva3dua2JVU1FwLWZuUXRtUzhWR010QnJGcC1qbF8yLXZwcE1ZQWExWG1GNmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1yamZsdEZOdVpQZXFwZ09NU1dUamFGSkk0cTdERDNIeGE3RENoYlFzck5qQjFCSGNKemMtZEdkSk5XRWhuWF9OUThzX25tZmZpSTNtbmU3WWhMdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 08:48:02 GMT</t>
+          <t>Thu, 30 Jul 2026 10:24:52 GMT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>에너지경제신문</t>
+          <t>v.daum.net</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>“증시 안정책 언제 내놓나”…저평가에도 코스피 외면하는 투자자들 [머니+]</t>
+          <t>최태원, SK하이닉스 주식 48억 규모 장내매수…"책임경영 차원"</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>긍정적 (호재)</t>
+          <t>중립</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1XWGtMb1hjS1FhamcxYWhIWlZpUV9saGdsOW9hQUdMeEQ0VTc4VzFoZFo3NTNTdVlwNkVZMnNQdWR1ODI3OF85ZlZFdVdhdmdxVm1lVWliYl9oYTF3ZXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE1URXB1M3dRWmlhbjJJYy05S053U1c5WG5pVnJva3dua2JVU1FwLWZuUXRtUzhWR010QnJGcC1qbF8yLXZwcE1ZQWExWG1GNmM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 06:49:33 GMT</t>
+          <t>Thu, 30 Jul 2026 08:48:02 GMT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>연합인포맥스</t>
+          <t>에너지경제신문</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[증시-마감] 코스피, 혼조세 후 하락 마감…개인 1.4조 순매도</t>
+          <t>“증시 안정책 언제 내놓나”…저평가에도 코스피 외면하는 투자자들 [머니+]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>부정적 (악재)</t>
+          <t>긍정적 (호재)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1zVnB1U3ZtV1I4LWlIZWt4QUxfTy1GakNVdVVEX3l0VlRoSndiZ1JnMFBhdjU3NEc2cXpUODZxM1J6akRUZWVsbnFEODVtVFk5dkJlRHlJZm9BV2haZXRHSjhkZXBvQXRaTV9ZaXlnRUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1XWGtMb1hjS1FhamcxYWhIWlZpUV9saGdsOW9hQUdMeEQ0VTc4VzFoZFo3NTNTdVlwNkVZMnNQdWR1ODI3OF85ZlZFdVdhdmdxVm1lVWliYl9oYTF3ZXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 09:09:00 GMT</t>
+          <t>Thu, 30 Jul 2026 06:49:33 GMT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ytn.co.kr</t>
+          <t>연합인포맥스</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[경제]연이틀 급락 후 또 하락...공포감에 개인은 투매</t>
+          <t>[증시-마감] 코스피, 혼조세 후 하락 마감…개인 1.4조 순매도</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3576,34 +3576,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE9HT1VxMUJzZEs1VlhkX1NzSTktSm92bHFtdnRSY2R0MHdnX0VWczM0ME5pUERtdEJlaVcybGgwNXNHNVZvQjcybTRnSFdhUzRvczd3Ny1lYmY5MmZHSlNPWE5XS0t4aU1LNmFQdTdBQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1zVnB1U3ZtV1I4LWlIZWt4QUxfTy1GakNVdVVEX3l0VlRoSndiZ1JnMFBhdjU3NEc2cXpUODZxM1J6akRUZWVsbnFEODVtVFk5dkJlRHlJZm9BV2haZXRHSjhkZXBvQXRaTV9ZaXlnRUk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 05:48:56 GMT</t>
+          <t>Thu, 30 Jul 2026 09:09:00 GMT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>ytn.co.kr</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>증권가와 테크 업계, "반도체 주가 급락? 공급 부족 본질은 여전히 유효"</t>
+          <t>[경제]연이틀 급락 후 또 하락...공포감에 개인은 투매</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>중립</t>
+          <t>부정적 (악재)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQcnZyVGlJdlF1MHBnelhmVG9GcThpVjhOSFRYTG1uTDlRajlHSGQ2eFBYbkFEU3BsMGpaeHpmMEVHY1B3c0hvT3FfRFBRemxFTzVQYnZ3SzlKZzhXQ1FGem04RFVqMTlQVUd2RDRLWFo0NmZNeXdkVnZ1YnpEZHlKcWJfcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE9HT1VxMUJzZEs1VlhkX1NzSTktSm92bHFtdnRSY2R0MHdnX0VWczM0ME5pUERtdEJlaVcybGgwNXNHNVZvQjcybTRnSFdhUzRvczd3Ny1lYmY5MmZHSlNPWE5XS0t4aU1LNmFQdTdBQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3637,17 +3637,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 06:42:41 GMT</t>
+          <t>Thu, 30 Jul 2026 05:48:56 GMT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>yna.co.kr</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>대신증권, 해외주식 잔고화면에 환차손익·매입환율 표시</t>
+          <t>증권가와 테크 업계, "반도체 주가 급락? 공급 부족 본질은 여전히 유효"</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1obE1VNUp4a0hJcVFKemQ3Z29ZN2xKeC1Yc2dwRmlTU0NJdjZTVHluRmhScDdLVjRvWWg2OWRsNTAxeHdpcXp6N0NnUDFucS1Gakd0ZGRiWmdYN03SAWBBVV95cUxNT2x6U0MxbHkxQUE2UUZhV2w1LVV1RHBBWFVPUWdkQVdpdk5NNFRHSzQ1ZnB3VE5saVowWTZmS0lNN0puMWpDMm54cS14aDhFQU56UzNoS1l6enRJdXBXVU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQcnZyVGlJdlF1MHBnelhmVG9GcThpVjhOSFRYTG1uTDlRajlHSGQ2eFBYbkFEU3BsMGpaeHpmMEVHY1B3c0hvT3FfRFBRemxFTzVQYnZ3SzlKZzhXQ1FGem04RFVqMTlQVUd2RDRLWFo0NmZNeXdkVnZ1YnpEZHlKcWJfcw?oc=5</t>
         </is>
       </c>
     </row>
